--- a/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\DPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\DPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819173F8-314B-44DF-BEC5-13FEFB698E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B6865C-6C6F-4230-B5F6-6E25430B93C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2850" yWindow="2850" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="DPbES" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DPbES!$A$1:$AK$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DPbES!$A$1:$AL$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -503,19 +503,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -525,30 +525,30 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
     </row>
   </sheetData>
@@ -562,113 +562,116 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AI25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AJ25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.7265625" customWidth="1"/>
+    <col min="2" max="3" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="2">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="2">
         <v>2021</v>
       </c>
-      <c r="C1" s="2">
+      <c r="D1" s="2">
         <v>2022</v>
       </c>
-      <c r="D1" s="2">
+      <c r="E1" s="2">
         <v>2023</v>
       </c>
-      <c r="E1" s="2">
+      <c r="F1" s="2">
         <v>2024</v>
       </c>
-      <c r="F1" s="2">
+      <c r="G1" s="2">
         <v>2025</v>
       </c>
-      <c r="G1" s="2">
+      <c r="H1" s="2">
         <v>2026</v>
       </c>
-      <c r="H1" s="2">
+      <c r="I1" s="2">
         <v>2027</v>
       </c>
-      <c r="I1" s="2">
+      <c r="J1" s="2">
         <v>2028</v>
       </c>
-      <c r="J1" s="2">
+      <c r="K1" s="2">
         <v>2029</v>
       </c>
-      <c r="K1" s="2">
+      <c r="L1" s="2">
         <v>2030</v>
       </c>
-      <c r="L1" s="2">
+      <c r="M1" s="2">
         <v>2031</v>
       </c>
-      <c r="M1" s="2">
+      <c r="N1" s="2">
         <v>2032</v>
       </c>
-      <c r="N1" s="2">
+      <c r="O1" s="2">
         <v>2033</v>
       </c>
-      <c r="O1" s="2">
+      <c r="P1" s="2">
         <v>2034</v>
       </c>
-      <c r="P1" s="2">
+      <c r="Q1" s="2">
         <v>2035</v>
       </c>
-      <c r="Q1" s="2">
+      <c r="R1" s="2">
         <v>2036</v>
       </c>
-      <c r="R1" s="2">
+      <c r="S1" s="2">
         <v>2037</v>
       </c>
-      <c r="S1" s="2">
+      <c r="T1" s="2">
         <v>2038</v>
       </c>
-      <c r="T1" s="2">
+      <c r="U1" s="2">
         <v>2039</v>
       </c>
-      <c r="U1" s="2">
+      <c r="V1" s="2">
         <v>2040</v>
       </c>
-      <c r="V1" s="2">
+      <c r="W1" s="2">
         <v>2041</v>
       </c>
-      <c r="W1" s="2">
+      <c r="X1" s="2">
         <v>2042</v>
       </c>
-      <c r="X1" s="2">
+      <c r="Y1" s="2">
         <v>2043</v>
       </c>
-      <c r="Y1" s="2">
+      <c r="Z1" s="2">
         <v>2044</v>
       </c>
-      <c r="Z1" s="2">
+      <c r="AA1" s="2">
         <v>2045</v>
       </c>
-      <c r="AA1" s="2">
+      <c r="AB1" s="2">
         <v>2046</v>
       </c>
-      <c r="AB1" s="2">
+      <c r="AC1" s="2">
         <v>2047</v>
       </c>
-      <c r="AC1" s="2">
+      <c r="AD1" s="2">
         <v>2048</v>
       </c>
-      <c r="AD1" s="2">
+      <c r="AE1" s="2">
         <v>2049</v>
       </c>
-      <c r="AE1" s="2">
+      <c r="AF1" s="2">
         <v>2050</v>
       </c>
-      <c r="AF1" s="2"/>
       <c r="AG1" s="2"/>
       <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ1" s="2"/>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -762,8 +765,11 @@
       <c r="AE2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -857,8 +863,11 @@
       <c r="AE3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -952,8 +961,11 @@
       <c r="AE4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1047,8 +1059,11 @@
       <c r="AE5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1142,8 +1157,11 @@
       <c r="AE6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1237,8 +1255,11 @@
       <c r="AE7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1332,8 +1353,11 @@
       <c r="AE8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1427,8 +1451,11 @@
       <c r="AE9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1522,8 +1549,11 @@
       <c r="AE10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1617,8 +1647,11 @@
       <c r="AE11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1712,8 +1745,11 @@
       <c r="AE12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1807,8 +1843,11 @@
       <c r="AE13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1902,8 +1941,11 @@
       <c r="AE14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1997,8 +2039,11 @@
       <c r="AE15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -2092,8 +2137,11 @@
       <c r="AE16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -2187,8 +2235,11 @@
       <c r="AE17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -2282,8 +2333,11 @@
       <c r="AE18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2377,8 +2431,11 @@
       <c r="AE19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2472,8 +2529,11 @@
       <c r="AE20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -2567,8 +2627,11 @@
       <c r="AE21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2662,8 +2725,11 @@
       <c r="AE22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2757,8 +2823,11 @@
       <c r="AE23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -2852,8 +2921,11 @@
       <c r="AE24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -2945,6 +3017,9 @@
         <v>0</v>
       </c>
       <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
         <v>0</v>
       </c>
     </row>
@@ -3098,6 +3173,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3106,20 +3187,37 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6483446-D7D1-40AD-ADC1-4B2C5D7E6D8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6483446-D7D1-40AD-ADC1-4B2C5D7E6D8D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E2ED42C-4D48-447F-9A3A-4944CC6F4A0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBA499C5-3ED5-437B-B881-1FD24686DA70}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBA499C5-3ED5-437B-B881-1FD24686DA70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E2ED42C-4D48-447F-9A3A-4944CC6F4A0E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>